--- a/data/trans_camb/IP1018-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Edad-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,0</t>
+          <t>-1,43; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,56</t>
+          <t>-0,91; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,0</t>
+          <t>-1,51; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,34; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,0</t>
+          <t>-0,97; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,23</t>
+          <t>-0,77; 0,24</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 0,0</t>
+          <t>-2,7; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,68</t>
+          <t>-2,03; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,19</t>
+          <t>-0,49; 1,16</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,0</t>
+          <t>-2,06; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,76</t>
+          <t>-1,61; 0,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,0</t>
+          <t>-1,02; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 0,34</t>
+          <t>-0,8; 0,34</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,0</t>
+          <t>-0,65; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,43</t>
+          <t>-0,35; 0,43</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; -0,07</t>
+          <t>-0,75; -0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,44</t>
+          <t>-0,45; 0,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; -0,09</t>
+          <t>-0,53; -0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,28</t>
+          <t>-0,28; 0,32</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,47; 328,82</t>
+          <t>-82,21; 395,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Edad-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,0</t>
+          <t>-1,3; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,56</t>
+          <t>-0,86; 0,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,0</t>
+          <t>-1,6; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,0</t>
+          <t>-1,55; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,0</t>
+          <t>-0,98; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,24</t>
+          <t>-0,76; 0,21</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,68</t>
+          <t>-2,04; 0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,0</t>
+          <t>-1,22; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,16</t>
+          <t>-0,55; 1,12</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,0</t>
+          <t>-2,16; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,67</t>
+          <t>-1,46; 0,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,34</t>
+          <t>-0,76; 0,34</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,0</t>
+          <t>-0,71; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 0,43</t>
+          <t>-0,4; 0,44</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,75; -0,07</t>
+          <t>-0,7; -0,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,46</t>
+          <t>-0,46; 0,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,09</t>
+          <t>-0,53; -0,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,32</t>
+          <t>-0,29; 0,36</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-82,21; 395,5</t>
+          <t>-78,66; 389,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1018-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1018-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -598,17 +598,17 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,46</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,28</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,0</t>
+          <t>-1,33; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>-1,45; 0,0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>-1,74; 0,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>-0,86; 0,56</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-1,6; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,55; 0,0</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,0</t>
+          <t>-0,95; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,21</t>
+          <t>-0,72; 0,23</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-2,6%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,58</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,17</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,68</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,58; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>-2,06; 0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,0</t>
+          <t>-1,14; 0,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,12</t>
+          <t>-0,49; 1,19</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-34,14%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,15; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,42; 0,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,0</t>
+          <t>-1,07; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,34</t>
+          <t>-0,75; 0,34</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-44,06%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-44,06%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,06</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>-0,73; -0,07</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-0,43; 0,44</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>-0,71; 0,0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>-0,4; 0,44</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,7; -0,07</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,45</t>
+          <t>-0,37; 0,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,53; -0,05</t>
+          <t>-0,54; -0,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,36</t>
+          <t>-0,28; 0,28</t>
         </is>
       </c>
     </row>
@@ -1298,17 +1298,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>-15,44%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>28,43%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-15,44%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-78,66; 389,53</t>
+          <t>-82,47; 328,82</t>
         </is>
       </c>
     </row>
